--- a/05-automation-vba/04-vba-functions-error-handling/5.4-vba-functions-error-handling.xlsx
+++ b/05-automation-vba/04-vba-functions-error-handling/5.4-vba-functions-error-handling.xlsx
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -325,7 +325,7 @@
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -337,25 +337,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -936,7 +933,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing your work with the answer key.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1037,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1081,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 591 rows — Excel Table 'tblPatients'</t>
+          <t>Data: 591 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1093,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 505 rows — Excel Table 'tblEncounters'</t>
+          <t>Data: 505 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1105,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 1,093 rows — Excel Table 'tblClaims'</t>
+          <t>Data: 1,093 rows, in the Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1117,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows — Excel Table 'tblPayers'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1165,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1182,7 +1179,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1253,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>A Function hands back a value by assigning it to its own name (BMI = …). Because it's Public and sits in a standard module, Excel lists it with the built-in functions, so =BMI( works in any cell. The return type is Variant so the same function can return a number or an error value made by CVErr. The two helpers come from the starter module: ArgValue turns a cell reference into its value, and IsNumberValue rejects blanks and text. Brenda Peterson weighs 180.4 lb at 61.8 in, so BMI = 703 × 180.4 ÷ 61.8² ≈ 33.21. If the cell shows #NAME?, the function isn't in a standard module of *this* workbook, or macros are disabled.</t>
+          <t>A Function hands back a value by assigning it to its own name (BMI = …). Because it's Public and sits in a standard module, Excel lists it with the built-in functions, so =BMI( works in any cell. The return type is Variant so the same function can return a number or an error value made by CVErr. The two helpers come from the starter module: ArgValue turns a cell reference into its value, and IsNumberValue rejects blanks and text. Brenda Peterson weighs 180.4 lb at 61.8 in, so BMI = 703 × 180.4 ÷ 61.8² ≈ 33.21. If the cell shows #NAME?, the function isn't in a standard module of this workbook, or macros are disabled.</t>
         </is>
       </c>
     </row>
@@ -1279,8 +1276,8 @@
           <t>=BMI([@WeightLb],[@HeightIn])</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="51">
-        <f t="array" ref="E6">SUMPRODUCT(--(703*'Patients'!$G$2:$G$592/'Patients'!$F$2:$F$592^2&gt;=30))</f>
+      <c r="E6" cm="1" s="19">
+        <f t="array" ref="E6">SUMPRODUCT(--(703*Patients!$G$2:$G$592/Patients!$F$2:$F$592^2&gt;=30))</f>
         <v/>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -1335,7 +1332,7 @@
         </is>
       </c>
       <c r="E7" cm="1" s="49">
-        <f t="array" ref="E7">SUMPRODUCT(YEAR('Encounters'!$E$2:$E$506)-YEAR('Encounters'!$D$2:$D$506)-(MONTH('Encounters'!$E$2:$E$506)*100+DAY('Encounters'!$E$2:$E$506)&lt;MONTH('Encounters'!$D$2:$D$506)*100+DAY('Encounters'!$D$2:$D$506)))/ROWS('Encounters'!$D$2:$D$506)</f>
+        <f t="array" ref="E7">SUMPRODUCT(YEAR(Encounters!$E$2:$E$506)-YEAR(Encounters!$D$2:$D$506)-(MONTH(Encounters!$E$2:$E$506)*100+DAY(Encounters!$E$2:$E$506)&lt;MONTH(Encounters!$D$2:$D$506)*100+DAY(Encounters!$D$2:$D$506)))/ROWS(Encounters!$D$2:$D$506)</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -1377,8 +1374,8 @@
 End Function</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="51">
-        <f t="array" ref="E8">SUMPRODUCT(('Encounters'!$F$2:$F$506&gt;='Encounters'!$E$2:$E$506)*(INT('Encounters'!$F$2:$F$506)-INT('Encounters'!$E$2:$E$506)))</f>
+      <c r="E8" cm="1" s="19">
+        <f t="array" ref="E8">SUMPRODUCT((Encounters!$F$2:$F$506&gt;=Encounters!$E$2:$E$506)*(INT(Encounters!$F$2:$F$506)-INT(Encounters!$E$2:$E$506)))</f>
         <v/>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -1406,8 +1403,8 @@
           <t>=COUNTIF(tblEncounters[LOSDays],"#VALUE!")</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="51">
-        <f t="array" ref="E9">SUMPRODUCT(--('Encounters'!$F$2:$F$506&lt;'Encounters'!$E$2:$E$506))</f>
+      <c r="E9" cm="1" s="19">
+        <f t="array" ref="E9">SUMPRODUCT(--(Encounters!$F$2:$F$506&lt;Encounters!$E$2:$E$506))</f>
         <v/>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -1427,7 +1424,7 @@
           <t>Write DENIALRATE(statusRange, [statusToCount]): the share of non-blank cells in statusRange whose text equals statusToCount (ignoring case). statusToCount is Optional and defaults to "Denied". Return #DIV/0! if the range has no non-blank cells. In the yellow cell, call DENIALRATE on the ClaimStatus column of the Claims sheet and leave out the second argument. The cell is already formatted as a percentage.</t>
         </is>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="51" t="n">
         <v>0.07685269899359561</v>
       </c>
       <c r="D10" s="48" t="inlineStr">
@@ -1451,8 +1448,8 @@
 End Function</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="53">
-        <f t="array" ref="E10">COUNTIF('Claims'!$H$2:$H$1094,"Denied")/COUNTA('Claims'!$H$2:$H$1094)</f>
+      <c r="E10" cm="1" s="52">
+        <f t="array" ref="E10">COUNTIF(Claims!$H$2:$H$1094,"Denied")/COUNTA(Claims!$H$2:$H$1094)</f>
         <v/>
       </c>
       <c r="F10" s="19" t="inlineStr">
@@ -1477,7 +1474,7 @@
       </c>
       <c r="D11" s="48" t="inlineStr">
         <is>
-          <t>Trace it: `AddFeeByVal charge` adds 25 to a **copy** (charge stays 100). `AddFeeByRef charge` adds 25 to the caller's variable itself (125). `AddFeeByRef (charge)` looks the same, but the parentheses turn `charge` into an expression, so VBA passes a temporary copy and charge stays **125**.</t>
+          <t>Trace it: AddFeeByVal charge adds 25 to a copy (charge stays 100). AddFeeByRef charge adds 25 to the caller's variable itself (125). AddFeeByRef (charge) looks the same, but the parentheses turn charge into an expression, so VBA passes a temporary copy and charge stays 125.</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -1532,8 +1529,8 @@
 End Function</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="51">
-        <f t="array" ref="E12">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Claims'!$I$2:$I$1094,'Claims'!$I$2:$I$1094&lt;&gt;"")))</f>
+      <c r="E12" cm="1" s="19">
+        <f t="array" ref="E12">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Claims!$I$2:$I$1094,Claims!$I$2:$I$1094&lt;&gt;"")))</f>
         <v/>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -1576,8 +1573,8 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="51">
-        <f t="array" ref="E13">ROWS(_xlfn.UNIQUE('Claims'!$B$2:$B$1094))</f>
+      <c r="E13" cm="1" s="19">
+        <f t="array" ref="E13">ROWS(_xlfn.UNIQUE(Claims!$B$2:$B$1094))</f>
         <v/>
       </c>
       <c r="F13" s="19" t="inlineStr">
@@ -1643,13 +1640,13 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="51">
-        <f t="array" ref="E14">INDEX('Payers'!$B$2:$B$9,MATCH(MAX(COUNTIFS('Claims'!$C$2:$C$1094,'Payers'!$A$2:$A$9,'Claims'!$H$2:$H$1094,"Denied")),COUNTIFS('Claims'!$C$2:$C$1094,'Payers'!$A$2:$A$9,'Claims'!$H$2:$H$1094,"Denied"),0))</f>
+      <c r="E14" cm="1" s="19">
+        <f t="array" ref="E14">INDEX(Payers!$B$2:$B$9,MATCH(MAX(COUNTIFS(Claims!$C$2:$C$1094,Payers!$A$2:$A$9,Claims!$H$2:$H$1094,"Denied")),COUNTIFS(Claims!$C$2:$C$1094,Payers!$A$2:$A$9,Claims!$H$2:$H$1094,"Denied"),0))</f>
         <v/>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>deniedCount(id) = deniedCount(id) + 1 is the counting pattern: reading a key that isn't there yet returns Empty (and quietly adds the key), and Empty + 1 = 1. Then one loop over .Keys keeps the largest count. The lookup dictionary replaces a VLOOKUP inside the loop. Note that the payer with the most claims overall is Medicare (270 claims), but the most *denials* come from Silverline Medicare Advantage: 22 of its 180 claims.</t>
+          <t>deniedCount(id) = deniedCount(id) + 1 is the counting pattern: reading a key that isn't there yet returns Empty (and quietly adds the key), and Empty + 1 = 1. Then one loop over .Keys keeps the largest count. The lookup dictionary replaces a VLOOKUP inside the loop. Note that the payer with the most claims overall is Medicare (270 claims), but the most denials come from Silverline Medicare Advantage: 22 of its 180 claims.</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1666,7 @@
       </c>
       <c r="D15" s="48" t="inlineStr">
         <is>
-          <t>CLng fails (run-time error 13, Type mismatch) on "abc" and on the empty string. Each time, VBA jumps to BadReading, prints a line, and `Resume Next` continues with the statement **after** the one that failed, which is `Next i`. So the bad items add nothing: 120 + 95 + 88 = **303**.</t>
+          <t>CLng fails (run-time error 13, Type mismatch) on "abc" and on the empty string. Each time, VBA jumps to BadReading, prints a line, and Resume Next continues with the statement after the one that failed, which is Next i. So the bad items add nothing: 120 + 95 + 88 = 303.</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -1699,7 +1696,7 @@
       </c>
       <c r="D16" s="48" t="inlineStr">
         <is>
-          <t>When `CLng("abc")` fails, the assignment never happens, so `reading` still holds 120 from the line before, and it's added again. The same thing happens for "" (reading is still 95). 120 + 120 + 95 + 95 + 88 = **518**.</t>
+          <t>When CLng("abc") fails, the assignment never happens, so reading still holds 120 from the line before, and it's added again. The same thing happens for "" (reading is still 95). 120 + 120 + 95 + 95 + 88 = 518.</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
@@ -1729,7 +1726,7 @@
       </c>
       <c r="D17" s="48" t="inlineStr">
         <is>
-          <t>`Application.Match` returns the error **value** Error 2042 (#N/A), which `IsError` detects, so the code prints "Application.Match: not found". `WorksheetFunction.Match` raises a run-time **error** instead: **1004**, *Unable to get the Match property of the WorksheetFunction class*.</t>
+          <t>Application.Match returns the error value Error 2042 (#N/A), which IsError detects, so the code prints "Application.Match: not found". WorksheetFunction.Match raises a run-time error instead: 1004, Unable to get the Match property of the WorksheetFunction class.</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
@@ -1766,7 +1763,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1780,7 +1777,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1974,8 +1971,8 @@
 End Function</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="51">
-        <f t="array" ref="E5">INDEX(_xlfn.SORTBY('Payers'!$B$2:$B$9,SUMIFS('Claims'!$E$2:$E$1094,'Claims'!$C$2:$C$1094,'Payers'!$A$2:$A$9),-1),3)</f>
+      <c r="E5" cm="1" s="19">
+        <f t="array" ref="E5">INDEX(_xlfn.SORTBY(Payers!$B$2:$B$9,SUMIFS(Claims!$E$2:$E$1094,Claims!$C$2:$C$1094,Payers!$A$2:$A$9),-1),3)</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -1995,16 +1992,16 @@
           <t>What DenialRate does your PayerSummary show for Silverline Medicare Advantage? (The gray cell finds Silverline's row on PayerSummary and reads column G.)</t>
         </is>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="51" t="n">
         <v>0.1129943502824859</v>
       </c>
       <c r="D6" s="48" t="inlineStr">
         <is>
-          <t>Read it from PayerSummary column G. Formula cross-check (blank and text amounts excluded): `=COUNTIFS(tblClaims[PayerID],"PY02",tblClaims[ClaimStatus],"Denied",tblClaims[BilledAmount],"&gt;=0")/COUNTIFS(tblClaims[PayerID],"PY02",tblClaims[BilledAmount],"&gt;=0")`</t>
-        </is>
-      </c>
-      <c r="E6" cm="1" s="53">
-        <f t="array" ref="E6">COUNTIFS('Claims'!$C$2:$C$1094,"PY02",'Claims'!$H$2:$H$1094,"Denied",'Claims'!$E$2:$E$1094,"&gt;=0")/COUNTIFS('Claims'!$C$2:$C$1094,"PY02",'Claims'!$E$2:$E$1094,"&gt;=0")</f>
+          <t>Read it from PayerSummary column G. Formula cross-check (blank and text amounts excluded): =COUNTIFS(tblClaims[PayerID],"PY02",tblClaims[ClaimStatus],"Denied",tblClaims[BilledAmount],"&gt;=0")/COUNTIFS(tblClaims[PayerID],"PY02",tblClaims[BilledAmount],"&gt;=0")</t>
+        </is>
+      </c>
+      <c r="E6" cm="1" s="52">
+        <f t="array" ref="E6">COUNTIFS(Claims!$C$2:$C$1094,"PY02",Claims!$H$2:$H$1094,"Denied",Claims!$E$2:$E$1094,"&gt;=0")/COUNTIFS(Claims!$C$2:$C$1094,"PY02",Claims!$E$2:$E$1094,"&gt;=0")</f>
         <v/>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -2024,16 +2021,16 @@
           <t>What total Paid does the TOTAL row of PayerSummary show? (The gray cell reads column E of the TOTAL row, and the check compares it to the cent.)</t>
         </is>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="53" t="n">
         <v>4440116.72</v>
       </c>
       <c r="D7" s="48" t="inlineStr">
         <is>
-          <t>Read it from the TOTAL row, column E. Formula cross-check: `=SUMIFS(tblClaims[PaidAmount],tblClaims[BilledAmount],"&gt;=0")`</t>
-        </is>
-      </c>
-      <c r="E7" cm="1" s="55">
-        <f t="array" ref="E7">SUMIFS('Claims'!$G$2:$G$1094,'Claims'!$E$2:$E$1094,"&gt;=0")</f>
+          <t>Read it from the TOTAL row, column E. Formula cross-check: =SUMIFS(tblClaims[PaidAmount],tblClaims[BilledAmount],"&gt;=0")</t>
+        </is>
+      </c>
+      <c r="E7" cm="1" s="54">
+        <f t="array" ref="E7">SUMIFS(Claims!$G$2:$G$1094,Claims!$E$2:$E$1094,"&gt;=0")</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -2058,11 +2055,11 @@
       </c>
       <c r="D8" s="48" t="inlineStr">
         <is>
-          <t>Read it from the cell next to *Rows skipped*. Formula cross-check: `=ROWS(tblClaims[BilledAmount])-COUNT(tblClaims[BilledAmount])`</t>
-        </is>
-      </c>
-      <c r="E8" cm="1" s="51">
-        <f t="array" ref="E8">ROWS('Claims'!$E$2:$E$1094)-COUNT('Claims'!$E$2:$E$1094)</f>
+          <t>Read it from the cell next to Rows skipped. Formula cross-check: =ROWS(tblClaims[BilledAmount])-COUNT(tblClaims[BilledAmount])</t>
+        </is>
+      </c>
+      <c r="E8" cm="1" s="19">
+        <f t="array" ref="E8">ROWS(Claims!$E$2:$E$1094)-COUNT(Claims!$E$2:$E$1094)</f>
         <v/>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -2071,7 +2068,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="306" customHeight="1">
+    <row r="9" ht="291" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -2085,9 +2082,9 @@
       <c r="C9" s="50" t="n"/>
       <c r="D9" s="48" t="inlineStr">
         <is>
-          <t>1. With Claims renamed, `SheetExists("Claims")` is False, so the macro shows the friendly MsgBox and exits **before** it changes any setting.
-2. With the header renamed, `HeaderColumn` raises error vbObjectError + 513. HeaderColumn has no handler of its own, so the error travels up to BuildPayerSummary's `Fail` handler, which shows *Column 'BilledAmount' was not found on sheet 'Claims'*. Then `Resume CleanExit` restores Calculation and ScreenUpdating.
-3. If Calculation Options shows Manual after the error, your error path skipped the cleanup block. Set it back with **Formulas → Calculation Options → Automatic**, then route the handler through `Resume CleanExit`. (Excel usually switches ScreenUpdating back on by itself when a macro ends, but the calculation mode stays manual for every open workbook until someone changes it.)</t>
+          <t>1. With Claims renamed, SheetExists("Claims") is False, so the macro shows the friendly MsgBox and exits before it changes any setting.
+2. With the header renamed, HeaderColumn raises error vbObjectError + 513. HeaderColumn has no handler of its own, so the error travels up to BuildPayerSummary's Fail handler, which shows Column 'BilledAmount' was not found on sheet 'Claims'. Then Resume CleanExit restores Calculation and ScreenUpdating.
+3. If Calculation Options shows Manual after the error, your error path skipped the cleanup block. Set it back with Formulas → Calculation Options → Automatic, then route the handler through Resume CleanExit. (Excel usually switches ScreenUpdating back on by itself when a macro ends, but the calculation mode stays manual for every open workbook until someone changes it.)</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -2220,7 +2217,7 @@
         </is>
       </c>
       <c r="D7" cm="1" s="23">
-        <f t="array" ref="D7">IF(COUNT('Patients'!$H$2:$H$592)=0,"",COUNTIF('Patients'!$H$2:$H$592,"&gt;=30"))</f>
+        <f t="array" ref="D7">IF(COUNT(Patients!$H$2:$H$592)=0,"",COUNTIF(Patients!$H$2:$H$592,"&gt;=30"))</f>
         <v/>
       </c>
       <c r="E7" s="22">
@@ -2245,7 +2242,7 @@
         </is>
       </c>
       <c r="D8" cm="1" s="24">
-        <f t="array" ref="D8">IF(COUNT('Encounters'!$G$2:$G$506)=0,"",AVERAGE('Encounters'!$G$2:$G$506))</f>
+        <f t="array" ref="D8">IF(COUNT(Encounters!$G$2:$G$506)=0,"",AVERAGE(Encounters!$G$2:$G$506))</f>
         <v/>
       </c>
       <c r="E8" s="22">
@@ -2270,7 +2267,7 @@
         </is>
       </c>
       <c r="D9" cm="1" s="23">
-        <f t="array" ref="D9">IF(COUNT('Encounters'!$H$2:$H$506)+SUMPRODUCT(--ISERROR('Encounters'!$H$2:$H$506))=0,"",_xlfn.AGGREGATE(9,6,'Encounters'!$H$2:$H$506))</f>
+        <f t="array" ref="D9">IF(COUNT(Encounters!$H$2:$H$506)+SUMPRODUCT(--ISERROR(Encounters!$H$2:$H$506))=0,"",_xlfn.AGGREGATE(9,6,Encounters!$H$2:$H$506))</f>
         <v/>
       </c>
       <c r="E9" s="22">
@@ -2295,7 +2292,7 @@
         </is>
       </c>
       <c r="D10" cm="1" s="23">
-        <f t="array" ref="D10">IF(COUNT('Encounters'!$H$2:$H$506)+SUMPRODUCT(--ISERROR('Encounters'!$H$2:$H$506))=0,"",COUNTIF('Encounters'!$H$2:$H$506,"#VALUE!"))</f>
+        <f t="array" ref="D10">IF(COUNT(Encounters!$H$2:$H$506)+SUMPRODUCT(--ISERROR(Encounters!$H$2:$H$506))=0,"",COUNTIF(Encounters!$H$2:$H$506,"#VALUE!"))</f>
         <v/>
       </c>
       <c r="E10" s="22">
@@ -74480,7 +74477,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="169" customHeight="1">
+    <row r="2" ht="154" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Cedar Ridge's revenue-cycle director wants a payer scorecard she can rebuild with one click every month. Write BuildPayerSummary (start from starter/PayerSummary.bas) so that it does five things:

--- a/05-automation-vba/04-vba-functions-error-handling/5.4-vba-functions-error-handling.xlsx
+++ b/05-automation-vba/04-vba-functions-error-handling/5.4-vba-functions-error-handling.xlsx
@@ -181,7 +181,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
+  <dimension ref="B2:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Expert  ·  about 65 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Expert  ·  about 185 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -921,7 +921,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type your answers for tasks 1, 6, 7, and 11–13 in the yellow cells. For tasks 2–5, fill the yellow UDF columns on the data sheets. For tasks 8–10, run your macros. The gray cells for those tasks fill in by themselves.</t>
         </is>
       </c>
     </row>
@@ -1076,70 +1076,94 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Patients</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 591 rows, in the Excel Table 'tblPatients'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Encounters</t>
+          <t>Patients</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 505 rows, in the Excel Table 'tblEncounters'</t>
+          <t>Data: 591 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Claims</t>
+          <t>Encounters</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 1,093 rows, in the Excel Table 'tblClaims'</t>
+          <t>Data: 505 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Data: 1,093 rows, in the Excel Table 'tblClaims'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>Payers</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Data: 8 rows, in the Excel Table 'tblPayers'</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Cedar Ridge Medical Center, 2025: adult patients with height and weight, inpatient and observation stays, every claim with its payer and status, and the 8 payers. A few rows contain deliberate data-entry errors for your code to catch.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Cedar Ridge Medical Center, 2025: adult patients with height and weight, inpatient and observation stays, every claim with its payer and status, and the 8 payers. A few rows contain deliberate data-entry errors for your code to catch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -2141,7 +2165,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
+          <t>Type your answers for tasks 1, 6, 7, and 11–13 in the yellow cells. The gray cells for tasks 2–5 and 8–10 fill in by themselves from your UDF columns and your macros. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
         </is>
       </c>
     </row>
@@ -73926,7 +73950,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00548235"/>
+    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -73948,7 +73972,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Don't type in column B. Run the macro named in column C and it fills the green cell. The gray cells on the Practice sheet read these cells.</t>
+          <t>Macros write into the blue cells. Don't type in column B: run the macro named in column C. The gray cells on the Practice sheet read these cells.</t>
         </is>
       </c>
     </row>
@@ -74492,7 +74516,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>There's nothing to type on this sheet. The gray cells for B1–B4 fill in once BuildPayerSummary has run, and the Check column turns green when they match. B5 is a test you run by hand, so compare your results with the key. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>

--- a/05-automation-vba/04-vba-functions-error-handling/5.4-vba-functions-error-handling.xlsx
+++ b/05-automation-vba/04-vba-functions-error-handling/5.4-vba-functions-error-handling.xlsx
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C37"/>
+  <dimension ref="B2:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Download the four .bas files in the lesson's starter/ folder (on GitHub, open each file and click Download raw file). Open the Visual Basic Editor with Alt + F11 (Mac: Option + F11), then choose File → Import File… for each one. HealthUDFs.bas is for tasks 1–6, ClaimDictionaries.bas for tasks 8–10, Snippets.bas for tasks 7 and 11–13, and PayerSummary.bas for the bonus.</t>
+          <t>Download the four .bas files in the lesson's starter/ folder (on GitHub, open each file and click Download raw file). Open the Visual Basic Editor with Alt + F11 (Mac: Option + F11, or Developer → Visual Basic), then choose File → Import File… for each one. HealthUDFs.bas is for tasks 1–6, ClaimDictionaries.bas for tasks 8–10, Snippets.bas for tasks 7 and 11–13, and PayerSummary.bas for the bonus.</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>The Output sheet is where your macros write their results. The Snippets sheet shows the code for the predict-the-output tasks. The bonus macro creates a PayerSummary sheet.</t>
+          <t>The bonus macro creates a PayerSummary sheet. The gray cells on the Bonus sheet read it, so they stay blank until the macro has run.</t>
         </is>
       </c>
     </row>
@@ -1136,34 +1136,58 @@
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>The bonus challenge (5 parts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1">
+          <t>Your macros for tasks 8–10 write their results here. The gray cells on Practice read them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>About the data</t>
+          <t>Snippets</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Cedar Ridge Medical Center, 2025: adult patients with height and weight, inpatient and observation stays, every claim with its payer and status, and the 8 payers. A few rows contain deliberate data-entry errors for your code to catch.</t>
+          <t>The code for the predict-the-output tasks 7 and 11–13 (the same code as starter/Snippets.bas).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Cedar Ridge Medical Center, 2025: adult patients with height and weight, inpatient and observation stays, every claim with its payer and status, and the 8 payers. A few rows contain deliberate data-entry errors for your code to catch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -1603,7 +1627,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>.Exists asks whether a key is already in the dictionary, so each PatientID is added once and .Count is the number of different patients. 1,093 claims come from 631 patients because 265 patients had more than one claim. Dim patients As Object with CreateObject is late binding: it needs no reference to the Scripting Runtime library, so the file works on any Windows PC. In Microsoft 365 the key's =ROWS(UNIQUE(…)) gives the same answer, but the dictionary pattern scales to jobs a formula can't do, like the bonus.</t>
+          <t>.Exists asks whether a key is already in the dictionary, so each PatientID is added once and .Count is the number of different patients. 1,093 claims come from 631 patients because 265 patients had more than one claim. Dim patients As Object with CreateObject is late binding: it needs no reference to the Scripting Runtime library, so the file works on any Windows PC. In Microsoft 365 and Excel 2021 or later, the key's =ROWS(UNIQUE(…)) gives the same answer, but the dictionary pattern scales to jobs a formula can't do, like the bonus.</t>
         </is>
       </c>
     </row>
